--- a/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
+++ b/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A7C4DF-883C-40C2-80F4-2509B6E80DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7C3AEE-7661-493E-9556-882A2D553AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="645" windowWidth="37170" windowHeight="19920" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -335,6 +335,7 @@
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Unit">_xlfn.LAMBDA("kg VS / head / day")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Variable">_xlfn.LAMBDA("VSj")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="VEERG_3_6_1_1__1_TotalAnnualMethaneFromEntericFermentationOtherLivestock_Result_Method1">'3.6.1.1-2 Enteric Methane'!$E$28</definedName>
     <definedName name="X_Cell_OtherLivestock_Others_Alpacas_Head">'Input - Other Livestock'!$F$26</definedName>
     <definedName name="X_Cell_OtherLivestock_Others_Camels_Head">'Input - Other Livestock'!$E$26</definedName>
     <definedName name="X_Cell_OtherLivestock_Others_Emus_Head">'Input - Other Livestock'!$I$26</definedName>
@@ -5153,7 +5154,7 @@
     <tableColumn id="1" xr3:uid="{D57CB9BE-4423-4B3C-8812-0053460E9FD4}" name="Other livestock type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{076CA99E-B6FF-4452-AA90-21B8618FF161}" name="Mj" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{076CA99E-B6FF-4452-AA90-21B8618FF161}" name="Mj" dataDxfId="55" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5215,49 +5216,49 @@
     <tableColumn id="1" xr3:uid="{3CD3D4D5-42BB-4E1C-8CE6-6F301EA89D3A}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{89C639A6-78BB-4857-8AFC-18317C27129F}" name="MAT" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{89C639A6-78BB-4857-8AFC-18317C27129F}" name="MAT" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B35E8617-3F4C-44F2-AE26-F6F52B9C3FDA}" name="MAP" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{B35E8617-3F4C-44F2-AE26-F6F52B9C3FDA}" name="MAP" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{DFA67CB4-1E4A-40B2-82BF-D41AFB94466B}" name="Frost days per year" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{DFA67CB4-1E4A-40B2-82BF-D41AFB94466B}" name="Frost days per year" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{334497DF-B010-4AB1-AAF8-2F8E84E9E77D}" name="Elevation" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{334497DF-B010-4AB1-AAF8-2F8E84E9E77D}" name="Elevation" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{47BDA440-B013-4AB4-9B72-4E65051E64CE}" name="MAP:PET" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{47BDA440-B013-4AB4-9B72-4E65051E64CE}" name="MAP:PET" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{7426E454-9049-497B-99DC-E7E205CEC2D8}" name="Min temp" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{7426E454-9049-497B-99DC-E7E205CEC2D8}" name="Min temp" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{93819F9B-35CE-419C-9552-6F61B8D5DF99}" name="Max temp" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{93819F9B-35CE-419C-9552-6F61B8D5DF99}" name="Max temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A12AB52B-8158-4DD8-AF9F-588DEE43A168}" name="Min rainfall" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{A12AB52B-8158-4DD8-AF9F-588DEE43A168}" name="Min rainfall" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{36B5A7A5-D8F3-4D06-8B7D-4C509C1D3E0C}" name="Max rainfall" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{36B5A7A5-D8F3-4D06-8B7D-4C509C1D3E0C}" name="Max rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{DFD7A042-FDBC-4D81-88AA-F6C20F0BDC28}" name="Min frost days" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{DFD7A042-FDBC-4D81-88AA-F6C20F0BDC28}" name="Min frost days" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E0353B4B-0F43-4BEA-9EDE-D807900D4DC5}" name="Max frost days" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{E0353B4B-0F43-4BEA-9EDE-D807900D4DC5}" name="Max frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5AA8BBA9-F6AB-4DFE-8FAA-FC1C9D2E7822}" name="Min elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{5AA8BBA9-F6AB-4DFE-8FAA-FC1C9D2E7822}" name="Min elevation" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{63E7711A-08D7-4F30-8EEA-B7FD061290B8}" name="Max elevation" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{63E7711A-08D7-4F30-8EEA-B7FD061290B8}" name="Max elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{CE79F652-DB30-4584-8987-D43C779A4CCE}" name="Min MAP:PET" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{CE79F652-DB30-4584-8987-D43C779A4CCE}" name="Min MAP:PET" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{2CE03279-D571-437B-B5E3-433363E8280D}" name="Max MAP:PET" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{2CE03279-D571-437B-B5E3-433363E8280D}" name="Max MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5275,7 +5276,7 @@
     <tableColumn id="1" xr3:uid="{EA988DAA-1D85-4AC0-BBEB-9D25F2947F14}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C243F783-F0D8-4C8B-B8BC-E2B796A4C087}" name="Wet or Dry Zone" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{C243F783-F0D8-4C8B-B8BC-E2B796A4C087}" name="Wet or Dry Zone" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5381,7 +5382,7 @@
     <tableColumn id="1" xr3:uid="{549F3560-2822-43EF-BBC6-4D437CAFA351}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C7951452-5EFF-4F3D-91FD-FFFB19AE4172}" name="FracWET" dataDxfId="39">
+    <tableColumn id="2" xr3:uid="{C7951452-5EFF-4F3D-91FD-FFFB19AE4172}" name="FracWET" dataDxfId="20">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5429,7 +5430,7 @@
     <tableColumn id="1" xr3:uid="{F5D7117F-EF5F-44B7-A497-DCF2CDF97AA6}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0175F786-6E03-4267-9719-1226C737AD44}" name="FracWET" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0175F786-6E03-4267-9719-1226C737AD44}" name="FracWET" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5438,16 +5439,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="17" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="54" dataCellStyle="Content normal">
   <autoFilter ref="D24:E32" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3E3B834E-0F7A-47D3-954A-A57B2234370A}" name="Other livestock type" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{3E3B834E-0F7A-47D3-954A-A57B2234370A}" name="Other livestock type" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0BCFF128-A246-43C6-BB57-DC9448A80579}" name="VSj" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0BCFF128-A246-43C6-BB57-DC9448A80579}" name="VSj" dataDxfId="52" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5465,7 +5466,7 @@
     <tableColumn id="1" xr3:uid="{7E38BE59-0C1B-4CC8-B71B-437EF9B0412A}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1AA60245-DAB4-4C67-B9DD-280CA895E668}" name="EFPRP" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1AA60245-DAB4-4C67-B9DD-280CA895E668}" name="EFPRP" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5483,7 +5484,7 @@
     <tableColumn id="1" xr3:uid="{3357157D-6C85-4223-8088-7194BFC7700C}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{71466C20-4100-4CCD-BEE3-D7B07653D619}" name="Season" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{71466C20-4100-4CCD-BEE3-D7B07653D619}" name="Season" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5515,49 +5516,49 @@
     <tableColumn id="1" xr3:uid="{72A76BA0-FF4C-47F3-8B5A-87E1951EA403}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{221102C9-4FC4-4F3F-B20B-7DFB76317D9D}" name="MAT (ºC)" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{221102C9-4FC4-4F3F-B20B-7DFB76317D9D}" name="MAT (ºC)" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F24468FF-0D84-4152-AD68-D9188BA490C9}" name="Anaerobic lagoon" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{F24468FF-0D84-4152-AD68-D9188BA490C9}" name="Anaerobic lagoon" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E8649CD1-A29B-4BFD-9347-E1C6304C5E1F}" name="Digester / covered lagoons" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{E8649CD1-A29B-4BFD-9347-E1C6304C5E1F}" name="Digester / covered lagoons" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3F2387FB-2089-443C-AA95-4E1FF7574E03}" name="Liquid systems" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{3F2387FB-2089-443C-AA95-4E1FF7574E03}" name="Liquid systems" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9D42539B-5B0F-40FE-BC2F-DAEFA90CA6A5}" name="Daily spread" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{9D42539B-5B0F-40FE-BC2F-DAEFA90CA6A5}" name="Daily spread" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89AB2F3D-5BBF-403E-9E90-89327CB43D0A}" name="Composting (passive windrow)" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{89AB2F3D-5BBF-403E-9E90-89327CB43D0A}" name="Composting (passive windrow)" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{972ABAC3-E6A5-48DC-9127-50F45FE5E6A0}" name="Solid storage" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{972ABAC3-E6A5-48DC-9127-50F45FE5E6A0}" name="Solid storage" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{53AEDE1C-2C1F-41DD-8F5B-B357264C42BA}" name="Pit storage" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{53AEDE1C-2C1F-41DD-8F5B-B357264C42BA}" name="Pit storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6ED6BA6A-4109-41A0-875E-6F3435604D43}" name="Deep litter" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{6ED6BA6A-4109-41A0-875E-6F3435604D43}" name="Deep litter" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8EE8EC8C-DEAD-444B-A70A-2E5B11E447C6}" name="Poultry manure with bedding" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{8EE8EC8C-DEAD-444B-A70A-2E5B11E447C6}" name="Poultry manure with bedding" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{0B0A9E69-134E-44C3-AA06-59DEEE76DC78}" name="Poultry manure without bedding" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{0B0A9E69-134E-44C3-AA06-59DEEE76DC78}" name="Poultry manure without bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{21D52C3E-5923-4A0C-8016-D394836BCE3D}" name="Direct processing" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{21D52C3E-5923-4A0C-8016-D394836BCE3D}" name="Direct processing" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{E9041A43-53A6-4257-B054-2C0E4105ADBF}" name="Direct application" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{E9041A43-53A6-4257-B054-2C0E4105ADBF}" name="Direct application" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{5BE2A21E-5B21-4D8D-91F5-07FCFC2F5ACC}" name="Pasture range and paddock" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{5BE2A21E-5B21-4D8D-91F5-07FCFC2F5ACC}" name="Pasture range and paddock" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D94301CB-CB36-4C48-983B-5400FAEB0CD0}" name="MAT raw" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{D94301CB-CB36-4C48-983B-5400FAEB0CD0}" name="MAT raw" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5575,7 +5576,7 @@
     <tableColumn id="1" xr3:uid="{2E9FAFA3-FB43-483E-8B26-B1275850A8BA}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CFB10182-5A87-4F72-968D-76E763E14ECA}" name="EFNi &amp; EFN2Oi" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{CFB10182-5A87-4F72-968D-76E763E14ECA}" name="EFNi &amp; EFN2Oi" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5591,7 +5592,7 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{20A20EB8-C627-4BE3-888B-C74000649A27}" name="Description" dataDxfId="19" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{20A20EB8-C627-4BE3-888B-C74000649A27}" name="Description" dataDxfId="0" dataCellStyle="Content normal"/>
     <tableColumn id="1" xr3:uid="{BFBD222F-7027-4744-A05A-47147627CE5E}" name="ID"/>
     <tableColumn id="3" xr3:uid="{E43655CB-F3D9-4DCF-9C07-EFF01E43E36A}" name="Score"/>
   </tableColumns>
@@ -5648,16 +5649,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="14" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="51" dataCellStyle="Content normal">
   <autoFilter ref="D39:E47" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{92CD5559-01AC-4144-B6DC-7F856864840C}" name="Other livestock type" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{92CD5559-01AC-4144-B6DC-7F856864840C}" name="Other livestock type" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A4955FC2-927B-4DF6-B94C-068E74A6FF39}" name="NEj" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A4955FC2-927B-4DF6-B94C-068E74A6FF39}" name="NEj" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5666,20 +5667,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="11" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="48" dataCellStyle="Content normal">
   <autoFilter ref="D54:F64" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{92B26601-57E2-4637-B097-133483C8744F}" name="Other livestock type" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{92B26601-57E2-4637-B097-133483C8744F}" name="Other livestock type" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6D10B565-469B-4476-91DD-3E192D501AEC}" name="Wco" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6D10B565-469B-4476-91DD-3E192D501AEC}" name="Wco" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4285ACF1-A507-45A9-B06F-3C8A119CF7C4}" name="Wco2" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{4285ACF1-A507-45A9-B06F-3C8A119CF7C4}" name="Wco2" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5688,20 +5689,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="7" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="44" dataCellStyle="Content normal">
   <autoFilter ref="D71:F79" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C1197CD-1D52-441D-BBC2-CD949C23252D}" name="Other livestock type" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{3C1197CD-1D52-441D-BBC2-CD949C23252D}" name="Other livestock type" dataDxfId="43" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8073D8FF-B3DA-4F6A-932F-294E074768D7}" name="Pasture range and paddock" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8073D8FF-B3DA-4F6A-932F-294E074768D7}" name="Pasture range and paddock" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BE446918-69F7-4B13-8457-24AF8D4D48BC}" name="Uncovered anaerobic lagoon" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{BE446918-69F7-4B13-8457-24AF8D4D48BC}" name="Uncovered anaerobic lagoon" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5710,20 +5711,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="3" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="40" dataCellStyle="Content normal">
   <autoFilter ref="D86:F94" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{378D0529-B2BA-4B26-B22D-9D5AE994C705}" name="Other livestock type" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{378D0529-B2BA-4B26-B22D-9D5AE994C705}" name="Other livestock type" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{614FC5E3-9067-4D7A-9048-5C785284F6FC}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{614FC5E3-9067-4D7A-9048-5C785284F6FC}" name="Pasture range and paddock" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9125F130-A695-42FD-984B-66D9A47F338B}" name="Uncovered anaerobic lagoon" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9125F130-A695-42FD-984B-66D9A47F338B}" name="Uncovered anaerobic lagoon" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11727,7 +11728,7 @@
         <v>95</v>
       </c>
       <c r="E7" s="82">
-        <f>'3.6.1.1-2 Enteric Methane'!E28</f>
+        <f>VEERG_3_6_1_1__1_TotalAnnualMethaneFromEntericFermentationOtherLivestock_Result_Method1</f>
         <v>630.69999999999993</v>
       </c>
       <c r="F7" s="82">

--- a/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
+++ b/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
@@ -432,9 +432,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -442,9 +442,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Automatically calculated, 12 months after start date</t>
@@ -573,9 +573,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -583,9 +583,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>DD/MM/YYYY or DD Month YYYY</t>
@@ -856,18 +856,18 @@
     <r>
       <rPr>
         <vertAlign val="subscript"/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>CO2e</t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve"> (Method 1)</t>
@@ -1048,115 +1048,113 @@
   </numFmts>
   <fonts count="58" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1167,269 +1165,264 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="10"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="18"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="16"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="4" tint="-0.249977111117893"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color theme="3" tint="9.9978637043366805E-2"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <vertAlign val="subscript"/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -2339,11 +2332,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2363,11 +2355,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2387,11 +2378,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2411,11 +2401,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2435,11 +2424,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2459,11 +2447,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2483,11 +2470,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2507,11 +2493,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2531,11 +2516,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2555,11 +2539,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2579,11 +2562,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2603,11 +2585,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2627,11 +2608,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2651,11 +2631,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2675,11 +2654,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2699,11 +2677,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2723,11 +2700,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2747,11 +2723,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2771,11 +2746,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2795,11 +2769,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2819,11 +2792,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2843,11 +2815,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2867,11 +2838,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2891,11 +2861,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2915,11 +2884,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2939,11 +2907,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2963,11 +2930,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2987,11 +2953,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3011,11 +2976,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3035,11 +2999,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3059,11 +3022,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3083,11 +3045,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3107,11 +3068,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3131,11 +3091,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3155,11 +3114,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3179,11 +3137,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3203,11 +3160,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3227,11 +3183,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3251,11 +3206,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3275,11 +3229,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3299,11 +3252,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3323,11 +3275,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3347,11 +3298,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3371,11 +3321,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3395,11 +3344,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3419,11 +3367,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3443,11 +3390,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3467,11 +3413,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3491,11 +3436,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3515,11 +3459,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3539,11 +3482,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3563,11 +3505,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3587,11 +3528,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3611,11 +3551,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3635,11 +3574,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3659,11 +3597,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3944,7 +3881,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4665,7 +4602,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1400" b="0">
+            <a:rPr lang="en-AU" sz="1200" b="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -4739,17 +4676,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{B9E89661-89DA-46FA-86B0-CDCD39DC2349}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Total annual methane production from enteric fermentation in other livestock</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000">
+          <a:endParaRPr lang="en-AU" sz="900">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -4865,14 +4802,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -4880,7 +4817,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑒𝑛𝑡𝑒𝑟𝑖𝑐</m:t>
@@ -4888,7 +4825,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -4898,14 +4835,14 @@
                         <m:chr m:val="∑"/>
                         <m:supHide m:val="on"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:naryPr>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑗</m:t>
@@ -4916,7 +4853,7 @@
                         <m:d>
                           <m:dPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -4925,14 +4862,14 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑁</m:t>
@@ -4940,7 +4877,7 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑗</m:t>
@@ -4948,7 +4885,7 @@
                               </m:sub>
                             </m:sSub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
@@ -4956,14 +4893,14 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑀</m:t>
@@ -4971,7 +4908,7 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑗</m:t>
@@ -4983,7 +4920,7 @@
                       </m:e>
                     </m:nary>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -4991,14 +4928,14 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>10</m:t>
@@ -5006,7 +4943,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−3</m:t>
@@ -5016,7 +4953,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5064,12 +5001,12 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_𝑒𝑛𝑡𝑒𝑟𝑖𝑐=∑8_𝑗▒(𝑁_𝑗×𝑀_𝑗 ) ×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5829,12 +5766,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -6045,31 +5982,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="105" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="104" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -6083,7 +6020,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71883A6B-B8DF-40B8-B36B-2098F8DD980B}">
   <dimension ref="A1:U165"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -6101,10 +6038,10 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -6128,225 +6065,225 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Other Livestock'!A1", "Other Livestock")</f>
         <v>Other Livestock</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'3.6.1.1-2 Enteric Methane'!A1", "3.6.1.1-2 Enteric Methane")</f>
         <v>3.6.1.1-2 Enteric Methane</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Other Livestock'!A1", "Constants - Other Livestock")</f>
         <v>Constants - Other Livestock</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="55" t="str">
         <f>HYPERLINK("#'Tab template'!A1", "Tab template")</f>
         <v>Tab template</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6358,7 +6295,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:BL82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="3" width="4.7109375" customWidth="1"/>
@@ -6402,7 +6339,7 @@
       <c r="AF1" s="92"/>
       <c r="AG1" s="92"/>
     </row>
-    <row r="2" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="92"/>
       <c r="D2" s="92"/>
       <c r="E2" s="92"/>
@@ -6435,7 +6372,7 @@
       <c r="AF2" s="92"/>
       <c r="AG2" s="92"/>
     </row>
-    <row r="3" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -6503,7 +6440,7 @@
       <c r="BK3" s="93"/>
       <c r="BL3" s="93"/>
     </row>
-    <row r="4" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="100" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -6571,7 +6508,7 @@
       <c r="BK4" s="21"/>
       <c r="BL4" s="21"/>
     </row>
-    <row r="5" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -6641,7 +6578,7 @@
       <c r="BK5" s="21"/>
       <c r="BL5" s="21"/>
     </row>
-    <row r="6" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1"/>
       <c r="D6" s="95" t="s">
         <v>94</v>
@@ -6707,7 +6644,7 @@
       <c r="BK6" s="21"/>
       <c r="BL6" s="21"/>
     </row>
-    <row r="7" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -6771,7 +6708,7 @@
       <c r="BK7" s="21"/>
       <c r="BL7" s="21"/>
     </row>
-    <row r="8" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
@@ -6838,7 +6775,7 @@
       <c r="BK8" s="21"/>
       <c r="BL8" s="21"/>
     </row>
-    <row r="9" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -6906,7 +6843,7 @@
       <c r="BK9" s="21"/>
       <c r="BL9" s="21"/>
     </row>
-    <row r="10" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Other Livestock'!A1", "Other Livestock")</f>
         <v>Other Livestock</v>
@@ -6974,7 +6911,7 @@
       <c r="BK10" s="21"/>
       <c r="BL10" s="21"/>
     </row>
-    <row r="11" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -7038,7 +6975,7 @@
       <c r="BK11" s="21"/>
       <c r="BL11" s="21"/>
     </row>
-    <row r="12" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -7102,7 +7039,7 @@
       <c r="BK12" s="21"/>
       <c r="BL12" s="21"/>
     </row>
-    <row r="13" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
@@ -7169,7 +7106,7 @@
       <c r="BK13" s="21"/>
       <c r="BL13" s="21"/>
     </row>
-    <row r="14" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'3.6.1.1-2 Enteric Methane'!A1", "3.6.1.1-2 Enteric Methane")</f>
         <v>3.6.1.1-2 Enteric Methane</v>
@@ -7237,7 +7174,7 @@
       <c r="BK14" s="21"/>
       <c r="BL14" s="21"/>
     </row>
-    <row r="15" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -7301,7 +7238,7 @@
       <c r="BK15" s="21"/>
       <c r="BL15" s="21"/>
     </row>
-    <row r="16" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -7365,7 +7302,7 @@
       <c r="BK16" s="21"/>
       <c r="BL16" s="21"/>
     </row>
-    <row r="17" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
         <v>1</v>
       </c>
@@ -7432,7 +7369,7 @@
       <c r="BK17" s="21"/>
       <c r="BL17" s="21"/>
     </row>
-    <row r="18" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Other Livestock'!A1", "Constants - Other Livestock")</f>
         <v>Constants - Other Livestock</v>
@@ -7500,7 +7437,7 @@
       <c r="BK18" s="21"/>
       <c r="BL18" s="21"/>
     </row>
-    <row r="19" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -7568,7 +7505,7 @@
       <c r="BK19" s="21"/>
       <c r="BL19" s="21"/>
     </row>
-    <row r="20" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -7636,7 +7573,7 @@
       <c r="BK20" s="21"/>
       <c r="BL20" s="21"/>
     </row>
-    <row r="21" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="str">
         <f>HYPERLINK("#'Tab template'!A1", "Tab template")</f>
         <v>Tab template</v>
@@ -7704,7 +7641,7 @@
       <c r="BK21" s="21"/>
       <c r="BL21" s="21"/>
     </row>
-    <row r="22" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -7768,7 +7705,7 @@
       <c r="BK22" s="21"/>
       <c r="BL22" s="21"/>
     </row>
-    <row r="23" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -7832,7 +7769,7 @@
       <c r="BK23" s="21"/>
       <c r="BL23" s="21"/>
     </row>
-    <row r="24" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -7896,7 +7833,7 @@
       <c r="BK24" s="21"/>
       <c r="BL24" s="21"/>
     </row>
-    <row r="25" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -7960,7 +7897,7 @@
       <c r="BK25" s="21"/>
       <c r="BL25" s="21"/>
     </row>
-    <row r="26" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -8024,7 +7961,7 @@
       <c r="BK26" s="21"/>
       <c r="BL26" s="21"/>
     </row>
-    <row r="27" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -8088,7 +8025,7 @@
       <c r="BK27" s="21"/>
       <c r="BL27" s="21"/>
     </row>
-    <row r="28" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -8152,7 +8089,7 @@
       <c r="BK28" s="21"/>
       <c r="BL28" s="21"/>
     </row>
-    <row r="29" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -8216,7 +8153,7 @@
       <c r="BK29" s="21"/>
       <c r="BL29" s="21"/>
     </row>
-    <row r="30" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -8280,7 +8217,7 @@
       <c r="BK30" s="21"/>
       <c r="BL30" s="21"/>
     </row>
-    <row r="31" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -8344,7 +8281,7 @@
       <c r="BK31" s="21"/>
       <c r="BL31" s="21"/>
     </row>
-    <row r="32" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -8408,7 +8345,7 @@
       <c r="BK32" s="21"/>
       <c r="BL32" s="21"/>
     </row>
-    <row r="33" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -8472,7 +8409,7 @@
       <c r="BK33" s="21"/>
       <c r="BL33" s="21"/>
     </row>
-    <row r="34" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -8536,7 +8473,7 @@
       <c r="BK34" s="21"/>
       <c r="BL34" s="21"/>
     </row>
-    <row r="35" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -8600,7 +8537,7 @@
       <c r="BK35" s="21"/>
       <c r="BL35" s="21"/>
     </row>
-    <row r="36" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -8664,7 +8601,7 @@
       <c r="BK36" s="21"/>
       <c r="BL36" s="21"/>
     </row>
-    <row r="37" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="21"/>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
@@ -8728,7 +8665,7 @@
       <c r="BK37" s="21"/>
       <c r="BL37" s="21"/>
     </row>
-    <row r="38" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="21"/>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
@@ -8792,7 +8729,7 @@
       <c r="BK38" s="21"/>
       <c r="BL38" s="21"/>
     </row>
-    <row r="39" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
       <c r="E39" s="21"/>
@@ -8856,7 +8793,7 @@
       <c r="BK39" s="21"/>
       <c r="BL39" s="21"/>
     </row>
-    <row r="40" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
@@ -8920,7 +8857,7 @@
       <c r="BK40" s="21"/>
       <c r="BL40" s="21"/>
     </row>
-    <row r="41" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
@@ -8984,7 +8921,7 @@
       <c r="BK41" s="21"/>
       <c r="BL41" s="21"/>
     </row>
-    <row r="42" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="21"/>
       <c r="D42" s="21"/>
       <c r="E42" s="21"/>
@@ -9048,7 +8985,7 @@
       <c r="BK42" s="21"/>
       <c r="BL42" s="21"/>
     </row>
-    <row r="43" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
@@ -9112,7 +9049,7 @@
       <c r="BK43" s="21"/>
       <c r="BL43" s="21"/>
     </row>
-    <row r="44" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
@@ -9176,7 +9113,7 @@
       <c r="BK44" s="21"/>
       <c r="BL44" s="21"/>
     </row>
-    <row r="45" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
@@ -9240,7 +9177,7 @@
       <c r="BK45" s="21"/>
       <c r="BL45" s="21"/>
     </row>
-    <row r="46" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
@@ -9304,7 +9241,7 @@
       <c r="BK46" s="21"/>
       <c r="BL46" s="21"/>
     </row>
-    <row r="47" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
@@ -9368,7 +9305,7 @@
       <c r="BK47" s="21"/>
       <c r="BL47" s="21"/>
     </row>
-    <row r="48" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
@@ -9432,7 +9369,7 @@
       <c r="BK48" s="21"/>
       <c r="BL48" s="21"/>
     </row>
-    <row r="49" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
@@ -9496,7 +9433,7 @@
       <c r="BK49" s="21"/>
       <c r="BL49" s="21"/>
     </row>
-    <row r="50" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
@@ -9560,7 +9497,7 @@
       <c r="BK50" s="21"/>
       <c r="BL50" s="21"/>
     </row>
-    <row r="51" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
@@ -9624,7 +9561,7 @@
       <c r="BK51" s="21"/>
       <c r="BL51" s="21"/>
     </row>
-    <row r="52" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
@@ -9688,7 +9625,7 @@
       <c r="BK52" s="21"/>
       <c r="BL52" s="21"/>
     </row>
-    <row r="53" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -9752,7 +9689,7 @@
       <c r="BK53" s="21"/>
       <c r="BL53" s="21"/>
     </row>
-    <row r="54" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
@@ -9816,7 +9753,7 @@
       <c r="BK54" s="21"/>
       <c r="BL54" s="21"/>
     </row>
-    <row r="55" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
@@ -9880,7 +9817,7 @@
       <c r="BK55" s="21"/>
       <c r="BL55" s="21"/>
     </row>
-    <row r="56" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
@@ -9944,7 +9881,7 @@
       <c r="BK56" s="21"/>
       <c r="BL56" s="21"/>
     </row>
-    <row r="57" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
@@ -10008,7 +9945,7 @@
       <c r="BK57" s="21"/>
       <c r="BL57" s="21"/>
     </row>
-    <row r="58" spans="3:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:64" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
@@ -10072,7 +10009,7 @@
       <c r="BK58" s="21"/>
       <c r="BL58" s="21"/>
     </row>
-    <row r="59" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
@@ -10136,7 +10073,7 @@
       <c r="BK59" s="21"/>
       <c r="BL59" s="21"/>
     </row>
-    <row r="60" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="21"/>
@@ -10200,7 +10137,7 @@
       <c r="BK60" s="21"/>
       <c r="BL60" s="21"/>
     </row>
-    <row r="61" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
@@ -10264,7 +10201,7 @@
       <c r="BK61" s="21"/>
       <c r="BL61" s="21"/>
     </row>
-    <row r="62" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
@@ -10328,7 +10265,7 @@
       <c r="BK62" s="21"/>
       <c r="BL62" s="21"/>
     </row>
-    <row r="63" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
@@ -10392,7 +10329,7 @@
       <c r="BK63" s="21"/>
       <c r="BL63" s="21"/>
     </row>
-    <row r="64" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
@@ -10456,7 +10393,7 @@
       <c r="BK64" s="21"/>
       <c r="BL64" s="21"/>
     </row>
-    <row r="65" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
@@ -10520,7 +10457,7 @@
       <c r="BK65" s="21"/>
       <c r="BL65" s="21"/>
     </row>
-    <row r="66" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
@@ -10584,7 +10521,7 @@
       <c r="BK66" s="21"/>
       <c r="BL66" s="21"/>
     </row>
-    <row r="67" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
@@ -10648,7 +10585,7 @@
       <c r="BK67" s="21"/>
       <c r="BL67" s="21"/>
     </row>
-    <row r="68" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
@@ -10712,7 +10649,7 @@
       <c r="BK68" s="21"/>
       <c r="BL68" s="21"/>
     </row>
-    <row r="69" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
@@ -10776,7 +10713,7 @@
       <c r="BK69" s="21"/>
       <c r="BL69" s="21"/>
     </row>
-    <row r="70" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C70" s="21"/>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
@@ -10840,7 +10777,7 @@
       <c r="BK70" s="21"/>
       <c r="BL70" s="21"/>
     </row>
-    <row r="71" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
@@ -10904,7 +10841,7 @@
       <c r="BK71" s="21"/>
       <c r="BL71" s="21"/>
     </row>
-    <row r="72" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C72" s="21"/>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
@@ -10968,7 +10905,7 @@
       <c r="BK72" s="21"/>
       <c r="BL72" s="21"/>
     </row>
-    <row r="73" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
@@ -11032,7 +10969,7 @@
       <c r="BK73" s="21"/>
       <c r="BL73" s="21"/>
     </row>
-    <row r="74" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C74" s="21"/>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
@@ -11096,7 +11033,7 @@
       <c r="BK74" s="21"/>
       <c r="BL74" s="21"/>
     </row>
-    <row r="75" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
@@ -11160,7 +11097,7 @@
       <c r="BK75" s="21"/>
       <c r="BL75" s="21"/>
     </row>
-    <row r="76" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C76" s="21"/>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
@@ -11224,7 +11161,7 @@
       <c r="BK76" s="21"/>
       <c r="BL76" s="21"/>
     </row>
-    <row r="77" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C77" s="21"/>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
@@ -11288,7 +11225,7 @@
       <c r="BK77" s="21"/>
       <c r="BL77" s="21"/>
     </row>
-    <row r="78" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C78" s="21"/>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
@@ -11352,7 +11289,7 @@
       <c r="BK78" s="21"/>
       <c r="BL78" s="21"/>
     </row>
-    <row r="79" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C79" s="21"/>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
@@ -11416,7 +11353,7 @@
       <c r="BK79" s="21"/>
       <c r="BL79" s="21"/>
     </row>
-    <row r="80" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C80" s="21"/>
       <c r="D80" s="21"/>
       <c r="E80" s="21"/>
@@ -11480,7 +11417,7 @@
       <c r="BK80" s="21"/>
       <c r="BL80" s="21"/>
     </row>
-    <row r="81" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C81" s="21"/>
       <c r="D81" s="21"/>
       <c r="E81" s="21"/>
@@ -11544,7 +11481,7 @@
       <c r="BK81" s="21"/>
       <c r="BL81" s="21"/>
     </row>
-    <row r="82" spans="3:64" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:64" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C82" s="21"/>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
@@ -11621,7 +11558,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:L87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="3" width="2.7109375" customWidth="1"/>
@@ -11643,10 +11580,10 @@
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="9"/>
     </row>
-    <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -11662,7 +11599,7 @@
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -11680,7 +11617,7 @@
       <c r="K4" s="6"/>
       <c r="L4" s="24"/>
     </row>
-    <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="100" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -11696,7 +11633,7 @@
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
     </row>
-    <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="21"/>
       <c r="D6" s="84" t="s">
         <v>62</v>
@@ -11722,7 +11659,7 @@
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
     </row>
-    <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="21"/>
       <c r="D7" s="1" t="s">
         <v>95</v>
@@ -11752,7 +11689,7 @@
       <c r="K7" s="21"/>
       <c r="L7" s="21"/>
     </row>
-    <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
@@ -11777,7 +11714,7 @@
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
     </row>
-    <row r="9" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -11793,7 +11730,7 @@
       <c r="K9" s="21"/>
       <c r="L9" s="21"/>
     </row>
-    <row r="10" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Other Livestock'!A1", "Other Livestock")</f>
         <v>Other Livestock</v>
@@ -11809,7 +11746,7 @@
       <c r="K10" s="21"/>
       <c r="L10" s="21"/>
     </row>
-    <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="21"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -11821,7 +11758,7 @@
       <c r="K11" s="21"/>
       <c r="L11" s="21"/>
     </row>
-    <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="21"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -11833,7 +11770,7 @@
       <c r="K12" s="21"/>
       <c r="L12" s="21"/>
     </row>
-    <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
@@ -11848,7 +11785,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'3.6.1.1-2 Enteric Methane'!A1", "3.6.1.1-2 Enteric Methane")</f>
         <v>3.6.1.1-2 Enteric Methane</v>
@@ -11864,7 +11801,7 @@
       <c r="K14" s="21"/>
       <c r="L14" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="21"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -11876,7 +11813,7 @@
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
     </row>
-    <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="21"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -11888,7 +11825,7 @@
       <c r="K16" s="21"/>
       <c r="L16" s="21"/>
     </row>
-    <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
         <v>1</v>
       </c>
@@ -11903,7 +11840,7 @@
       <c r="K17" s="21"/>
       <c r="L17" s="21"/>
     </row>
-    <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Other Livestock'!A1", "Constants - Other Livestock")</f>
         <v>Constants - Other Livestock</v>
@@ -11919,7 +11856,7 @@
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
     </row>
-    <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -11935,7 +11872,7 @@
       <c r="K19" s="21"/>
       <c r="L19" s="21"/>
     </row>
-    <row r="20" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -11951,7 +11888,7 @@
       <c r="K20" s="21"/>
       <c r="L20" s="21"/>
     </row>
-    <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="str">
         <f>HYPERLINK("#'Tab template'!A1", "Tab template")</f>
         <v>Tab template</v>
@@ -11967,7 +11904,7 @@
       <c r="K21" s="21"/>
       <c r="L21" s="21"/>
     </row>
-    <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="21"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -11979,7 +11916,7 @@
       <c r="K22" s="21"/>
       <c r="L22" s="21"/>
     </row>
-    <row r="23" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="21"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -11991,7 +11928,7 @@
       <c r="K23" s="21"/>
       <c r="L23" s="21"/>
     </row>
-    <row r="24" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="21"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -12003,7 +11940,7 @@
       <c r="K24" s="21"/>
       <c r="L24" s="21"/>
     </row>
-    <row r="25" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="21"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -12015,7 +11952,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="26" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="21"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -12027,7 +11964,7 @@
       <c r="K26" s="21"/>
       <c r="L26" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="21"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -12039,7 +11976,7 @@
       <c r="K27" s="21"/>
       <c r="L27" s="21"/>
     </row>
-    <row r="28" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="21"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -12051,7 +11988,7 @@
       <c r="K28" s="21"/>
       <c r="L28" s="21"/>
     </row>
-    <row r="29" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="21"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -12063,7 +12000,7 @@
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
     </row>
-    <row r="30" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="21"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -12075,7 +12012,7 @@
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
     </row>
-    <row r="31" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="21"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -12087,7 +12024,7 @@
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
     </row>
-    <row r="32" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="21"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -12099,7 +12036,7 @@
       <c r="K32" s="21"/>
       <c r="L32" s="21"/>
     </row>
-    <row r="33" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="21"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -12111,7 +12048,7 @@
       <c r="K33" s="21"/>
       <c r="L33" s="21"/>
     </row>
-    <row r="34" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="21"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -12123,7 +12060,7 @@
       <c r="K34" s="21"/>
       <c r="L34" s="21"/>
     </row>
-    <row r="35" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="21"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -12135,7 +12072,7 @@
       <c r="K35" s="21"/>
       <c r="L35" s="21"/>
     </row>
-    <row r="36" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="21"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -12147,7 +12084,7 @@
       <c r="K36" s="21"/>
       <c r="L36" s="21"/>
     </row>
-    <row r="37" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="21"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -12159,7 +12096,7 @@
       <c r="K37" s="21"/>
       <c r="L37" s="21"/>
     </row>
-    <row r="38" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="21"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -12171,7 +12108,7 @@
       <c r="K38" s="81"/>
       <c r="L38" s="21"/>
     </row>
-    <row r="39" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="21"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -12183,7 +12120,7 @@
       <c r="K39" s="81"/>
       <c r="L39" s="21"/>
     </row>
-    <row r="40" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="21"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -12195,7 +12132,7 @@
       <c r="K40" s="81"/>
       <c r="L40" s="21"/>
     </row>
-    <row r="41" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="21"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -12207,7 +12144,7 @@
       <c r="K41" s="81"/>
       <c r="L41" s="21"/>
     </row>
-    <row r="42" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="21"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -12219,7 +12156,7 @@
       <c r="K42" s="81"/>
       <c r="L42" s="21"/>
     </row>
-    <row r="43" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="21"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -12231,7 +12168,7 @@
       <c r="K43" s="81"/>
       <c r="L43" s="21"/>
     </row>
-    <row r="44" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="21"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -12243,7 +12180,7 @@
       <c r="K44" s="81"/>
       <c r="L44" s="21"/>
     </row>
-    <row r="45" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="21"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -12255,7 +12192,7 @@
       <c r="K45" s="81"/>
       <c r="L45" s="21"/>
     </row>
-    <row r="46" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="21"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -12267,7 +12204,7 @@
       <c r="K46" s="81"/>
       <c r="L46" s="21"/>
     </row>
-    <row r="47" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="21"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -12279,7 +12216,7 @@
       <c r="K47" s="81"/>
       <c r="L47" s="21"/>
     </row>
-    <row r="48" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="21"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -12291,7 +12228,7 @@
       <c r="K48" s="81"/>
       <c r="L48" s="21"/>
     </row>
-    <row r="49" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="21"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -12303,7 +12240,7 @@
       <c r="K49" s="81"/>
       <c r="L49" s="21"/>
     </row>
-    <row r="50" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="21"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -12315,7 +12252,7 @@
       <c r="K50" s="81"/>
       <c r="L50" s="21"/>
     </row>
-    <row r="51" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="21"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -12327,7 +12264,7 @@
       <c r="K51" s="81"/>
       <c r="L51" s="21"/>
     </row>
-    <row r="52" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="21"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -12339,7 +12276,7 @@
       <c r="K52" s="81"/>
       <c r="L52" s="21"/>
     </row>
-    <row r="53" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="21"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -12351,7 +12288,7 @@
       <c r="K53" s="81"/>
       <c r="L53" s="21"/>
     </row>
-    <row r="54" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="21"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -12363,7 +12300,7 @@
       <c r="K54" s="21"/>
       <c r="L54" s="21"/>
     </row>
-    <row r="55" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="21"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -12375,7 +12312,7 @@
       <c r="K55" s="21"/>
       <c r="L55" s="21"/>
     </row>
-    <row r="56" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="21"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -12387,7 +12324,7 @@
       <c r="K56" s="21"/>
       <c r="L56" s="21"/>
     </row>
-    <row r="57" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="21"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -12399,7 +12336,7 @@
       <c r="K57" s="21"/>
       <c r="L57" s="21"/>
     </row>
-    <row r="58" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="21"/>
       <c r="D58" s="1"/>
       <c r="E58" s="29"/>
@@ -12411,7 +12348,7 @@
       <c r="K58" s="21"/>
       <c r="L58" s="21"/>
     </row>
-    <row r="59" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="21"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -12423,7 +12360,7 @@
       <c r="K59" s="1"/>
       <c r="L59" s="21"/>
     </row>
-    <row r="60" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="21"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -12435,7 +12372,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="21"/>
     </row>
-    <row r="61" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="21"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -12447,7 +12384,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="21"/>
     </row>
-    <row r="62" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="21"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -12459,7 +12396,7 @@
       <c r="K62" s="1"/>
       <c r="L62" s="21"/>
     </row>
-    <row r="63" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="21"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -12471,7 +12408,7 @@
       <c r="K63" s="1"/>
       <c r="L63" s="21"/>
     </row>
-    <row r="64" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="21"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -12483,7 +12420,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="21"/>
     </row>
-    <row r="65" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="21"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -12495,7 +12432,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="21"/>
     </row>
-    <row r="66" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="21"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -12507,7 +12444,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="21"/>
     </row>
-    <row r="67" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="21"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -12519,7 +12456,7 @@
       <c r="K67" s="1"/>
       <c r="L67" s="21"/>
     </row>
-    <row r="68" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="21"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -12531,7 +12468,7 @@
       <c r="K68" s="1"/>
       <c r="L68" s="21"/>
     </row>
-    <row r="69" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="21"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -12543,7 +12480,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="21"/>
     </row>
-    <row r="70" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="21"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -12555,7 +12492,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="21"/>
     </row>
-    <row r="71" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="21"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -12567,7 +12504,7 @@
       <c r="K71" s="1"/>
       <c r="L71" s="21"/>
     </row>
-    <row r="72" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="21"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -12579,7 +12516,7 @@
       <c r="K72" s="1"/>
       <c r="L72" s="21"/>
     </row>
-    <row r="73" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="21"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -12591,7 +12528,7 @@
       <c r="K73" s="1"/>
       <c r="L73" s="21"/>
     </row>
-    <row r="74" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="21"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -12603,7 +12540,7 @@
       <c r="K74" s="1"/>
       <c r="L74" s="21"/>
     </row>
-    <row r="75" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="21"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -12615,7 +12552,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="21"/>
     </row>
-    <row r="76" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C76" s="21"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -12627,7 +12564,7 @@
       <c r="K76" s="1"/>
       <c r="L76" s="21"/>
     </row>
-    <row r="77" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C77" s="21"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -12639,7 +12576,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="21"/>
     </row>
-    <row r="78" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C78" s="21"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -12651,7 +12588,7 @@
       <c r="K78" s="1"/>
       <c r="L78" s="21"/>
     </row>
-    <row r="79" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C79" s="21"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -12663,7 +12600,7 @@
       <c r="K79" s="1"/>
       <c r="L79" s="21"/>
     </row>
-    <row r="80" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C80" s="21"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -12675,7 +12612,7 @@
       <c r="K80" s="1"/>
       <c r="L80" s="21"/>
     </row>
-    <row r="81" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C81" s="21"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -12687,7 +12624,7 @@
       <c r="K81" s="1"/>
       <c r="L81" s="21"/>
     </row>
-    <row r="82" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C82" s="21"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -12699,7 +12636,7 @@
       <c r="K82" s="1"/>
       <c r="L82" s="21"/>
     </row>
-    <row r="83" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C83" s="21"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -12711,7 +12648,7 @@
       <c r="K83" s="1"/>
       <c r="L83" s="21"/>
     </row>
-    <row r="84" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C84" s="21"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -12723,7 +12660,7 @@
       <c r="K84" s="1"/>
       <c r="L84" s="21"/>
     </row>
-    <row r="85" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C85" s="21"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -12735,7 +12672,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="21"/>
     </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C86" s="21"/>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
@@ -12747,7 +12684,7 @@
       <c r="K86" s="21"/>
       <c r="L86" s="21"/>
     </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C87" s="21"/>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
@@ -12772,7 +12709,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AA160"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="16" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="7" customWidth="1"/>
@@ -12793,7 +12730,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -12804,7 +12741,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -12831,7 +12768,7 @@
       <c r="W3" s="11"/>
       <c r="X3" s="11"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -12846,7 +12783,7 @@
       <c r="J4" s="56"/>
       <c r="K4" s="56"/>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -12856,12 +12793,12 @@
       </c>
       <c r="N5" s="37"/>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="D6" s="14"/>
       <c r="N6" s="38"/>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
       <c r="D7" s="1" t="s">
         <v>4</v>
@@ -12871,7 +12808,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
@@ -12882,14 +12819,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="99" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
       <c r="N9" s="39"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Other Livestock'!A1", "Other Livestock")</f>
         <v>Other Livestock</v>
@@ -12902,11 +12839,11 @@
       <c r="G10" s="68"/>
       <c r="N10" s="39"/>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="N11" s="40"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="10" t="s">
         <v>57</v>
@@ -12918,7 +12855,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
@@ -12935,7 +12872,7 @@
       <c r="N13" s="35"/>
       <c r="O13" s="35"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'3.6.1.1-2 Enteric Methane'!A1", "3.6.1.1-2 Enteric Methane")</f>
         <v>3.6.1.1-2 Enteric Methane</v>
@@ -12943,7 +12880,7 @@
       <c r="N14" s="35"/>
       <c r="O14" s="35"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
       <c r="D15" s="31"/>
       <c r="E15" s="31"/>
@@ -12956,7 +12893,7 @@
       <c r="N15" s="35"/>
       <c r="O15" s="35"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
@@ -12969,7 +12906,7 @@
       <c r="N16" s="35"/>
       <c r="O16" s="35"/>
     </row>
-    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
         <v>1</v>
       </c>
@@ -12982,7 +12919,7 @@
       <c r="J17" s="31"/>
       <c r="K17" s="31"/>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Other Livestock'!A1", "Constants - Other Livestock")</f>
         <v>Constants - Other Livestock</v>
@@ -12996,7 +12933,7 @@
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
     </row>
-    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -13011,7 +12948,7 @@
       <c r="K19" s="31"/>
       <c r="N19" s="37"/>
     </row>
-    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -13026,7 +12963,7 @@
       <c r="K20" s="31"/>
       <c r="N20" s="38"/>
     </row>
-    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="str">
         <f>HYPERLINK("#'Tab template'!A1", "Tab template")</f>
         <v>Tab template</v>
@@ -13040,7 +12977,7 @@
       <c r="J21" s="31"/>
       <c r="K21" s="31"/>
     </row>
-    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="31"/>
       <c r="E22" s="31"/>
@@ -13051,7 +12988,7 @@
       <c r="J22" s="31"/>
       <c r="K22" s="31"/>
     </row>
-    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="31"/>
       <c r="E23" s="31"/>
@@ -13062,7 +12999,7 @@
       <c r="J23" s="31"/>
       <c r="K23" s="31"/>
     </row>
-    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="31"/>
       <c r="E24" s="31"/>
@@ -13073,7 +13010,7 @@
       <c r="J24" s="31"/>
       <c r="K24" s="31"/>
     </row>
-    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
@@ -13085,7 +13022,7 @@
       <c r="K25" s="31"/>
       <c r="N25" s="38"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
@@ -13096,7 +13033,7 @@
       <c r="J26" s="31"/>
       <c r="K26" s="31"/>
     </row>
-    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="31"/>
       <c r="E27" s="31"/>
@@ -13107,7 +13044,7 @@
       <c r="J27" s="31"/>
       <c r="K27" s="31"/>
     </row>
-    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="31"/>
       <c r="E28" s="31"/>
@@ -13118,7 +13055,7 @@
       <c r="J28" s="31"/>
       <c r="K28" s="31"/>
     </row>
-    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="31"/>
       <c r="E29" s="31"/>
@@ -13129,7 +13066,7 @@
       <c r="J29" s="31"/>
       <c r="K29" s="31"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="31"/>
       <c r="E30" s="31"/>
@@ -13154,7 +13091,7 @@
       <c r="X30" s="43"/>
       <c r="Y30" s="43"/>
     </row>
-    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="D31" s="31"/>
       <c r="E31" s="31"/>
@@ -13179,7 +13116,7 @@
       <c r="X31" s="42"/>
       <c r="Y31" s="42"/>
     </row>
-    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="D32" s="31"/>
       <c r="E32" s="31"/>
@@ -13204,7 +13141,7 @@
       <c r="X32" s="42"/>
       <c r="Y32" s="42"/>
     </row>
-    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
@@ -13229,7 +13166,7 @@
       <c r="X33" s="42"/>
       <c r="Y33" s="42"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="31"/>
       <c r="E34" s="31"/>
@@ -13254,7 +13191,7 @@
       <c r="X34" s="42"/>
       <c r="Y34" s="42"/>
     </row>
-    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="31"/>
       <c r="E35" s="31"/>
@@ -13279,7 +13216,7 @@
       <c r="X35" s="42"/>
       <c r="Y35" s="42"/>
     </row>
-    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="31"/>
       <c r="E36" s="31"/>
@@ -13304,7 +13241,7 @@
       <c r="X36" s="42"/>
       <c r="Y36" s="42"/>
     </row>
-    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="31"/>
       <c r="E37" s="31"/>
@@ -13329,7 +13266,7 @@
       <c r="X37" s="42"/>
       <c r="Y37" s="42"/>
     </row>
-    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="31"/>
       <c r="E38" s="31"/>
@@ -13354,7 +13291,7 @@
       <c r="X38" s="42"/>
       <c r="Y38" s="42"/>
     </row>
-    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="31"/>
       <c r="E39" s="31"/>
@@ -13379,7 +13316,7 @@
       <c r="X39" s="42"/>
       <c r="Y39" s="42"/>
     </row>
-    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="31"/>
       <c r="E40" s="31"/>
@@ -13404,7 +13341,7 @@
       <c r="X40" s="44"/>
       <c r="Y40" s="44"/>
     </row>
-    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="31"/>
       <c r="E41" s="31"/>
@@ -13415,7 +13352,7 @@
       <c r="J41" s="31"/>
       <c r="K41" s="31"/>
     </row>
-    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="31"/>
       <c r="E42" s="31"/>
@@ -13426,7 +13363,7 @@
       <c r="J42" s="31"/>
       <c r="K42" s="31"/>
     </row>
-    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="31"/>
       <c r="E43" s="31"/>
@@ -13437,7 +13374,7 @@
       <c r="J43" s="31"/>
       <c r="K43" s="31"/>
     </row>
-    <row r="44" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
       <c r="D44" s="31"/>
       <c r="E44" s="31"/>
@@ -13448,7 +13385,7 @@
       <c r="J44" s="31"/>
       <c r="K44" s="31"/>
     </row>
-    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="31"/>
       <c r="E45" s="31"/>
@@ -13459,7 +13396,7 @@
       <c r="J45" s="31"/>
       <c r="K45" s="31"/>
     </row>
-    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="31"/>
       <c r="E46" s="31"/>
@@ -13470,7 +13407,7 @@
       <c r="J46" s="31"/>
       <c r="K46" s="31"/>
     </row>
-    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="31"/>
       <c r="E47" s="31"/>
@@ -13481,7 +13418,7 @@
       <c r="J47" s="31"/>
       <c r="K47" s="31"/>
     </row>
-    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="31"/>
       <c r="E48" s="31"/>
@@ -13492,7 +13429,7 @@
       <c r="J48" s="31"/>
       <c r="K48" s="31"/>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="31"/>
       <c r="E49" s="31"/>
@@ -13500,7 +13437,7 @@
       <c r="G49" s="32"/>
       <c r="H49" s="31"/>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="31"/>
       <c r="E50" s="31"/>
@@ -13508,7 +13445,7 @@
       <c r="G50" s="32"/>
       <c r="H50" s="31"/>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="58"/>
       <c r="E51" s="59"/>
@@ -13516,76 +13453,76 @@
       <c r="G51" s="59"/>
       <c r="H51" s="60"/>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="G54" s="61"/>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
       <c r="D55" s="6"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="20"/>
       <c r="F57" s="62"/>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="1"/>
       <c r="E58" s="63"/>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="1"/>
       <c r="E59" s="63"/>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="1"/>
       <c r="E60" s="64"/>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="20"/>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="1"/>
       <c r="E64" s="63"/>
     </row>
-    <row r="65" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="1"/>
       <c r="E65" s="63"/>
     </row>
-    <row r="66" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="1"/>
       <c r="E66" s="64"/>
     </row>
-    <row r="67" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
     </row>
-    <row r="68" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
     </row>
-    <row r="69" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="51"/>
       <c r="E69" s="51"/>
@@ -13594,7 +13531,7 @@
       <c r="H69" s="51"/>
       <c r="I69" s="51"/>
     </row>
-    <row r="70" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="51"/>
       <c r="E70" s="51"/>
@@ -13603,7 +13540,7 @@
       <c r="H70" s="51"/>
       <c r="I70" s="51"/>
     </row>
-    <row r="71" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="51"/>
       <c r="E71" s="51"/>
@@ -13612,7 +13549,7 @@
       <c r="H71" s="51"/>
       <c r="I71" s="51"/>
     </row>
-    <row r="72" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="51"/>
       <c r="E72" s="51"/>
@@ -13621,273 +13558,273 @@
       <c r="H72" s="51"/>
       <c r="I72" s="51"/>
     </row>
-    <row r="73" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
     </row>
-    <row r="74" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
     </row>
-    <row r="75" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
     </row>
-    <row r="76" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
     </row>
-    <row r="77" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
     </row>
-    <row r="78" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
       <c r="D78" s="65"/>
     </row>
-    <row r="79" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
       <c r="D79" s="65"/>
     </row>
-    <row r="80" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
       <c r="D80" s="65"/>
     </row>
-    <row r="81" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="65"/>
     </row>
-    <row r="82" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="65"/>
     </row>
-    <row r="83" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
     </row>
-    <row r="84" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
     </row>
-    <row r="86" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
     </row>
-    <row r="87" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
     </row>
-    <row r="88" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
     </row>
-    <row r="90" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
     </row>
-    <row r="91" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
     </row>
-    <row r="92" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
     </row>
-    <row r="93" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
     </row>
-    <row r="94" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
     </row>
-    <row r="95" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
     </row>
-    <row r="96" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
     </row>
-    <row r="97" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
     </row>
-    <row r="98" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
     </row>
-    <row r="100" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
     </row>
-    <row r="102" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
     </row>
-    <row r="104" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
     </row>
-    <row r="113" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A116"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A117"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A118"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A119"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A120"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A121"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A122"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A124"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A125"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A127"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A128"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A129"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A132"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A133"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A134"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A135"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A136"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A138"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A139"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A140"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A141"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A142"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A143"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A144"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A145"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A146"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A147"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A148"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A149"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A150"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A151"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A152"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A153"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A154"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A155"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A156"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A157"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A158"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A160"/>
     </row>
   </sheetData>
@@ -13902,7 +13839,7 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:U165"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -13932,7 +13869,7 @@
       <c r="T1" s="50"/>
       <c r="U1" s="50"/>
     </row>
-    <row r="2" spans="1:21" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="N2" s="50"/>
       <c r="O2" s="50"/>
@@ -13943,7 +13880,7 @@
       <c r="T2" s="50"/>
       <c r="U2" s="50"/>
     </row>
-    <row r="3" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -13959,13 +13896,13 @@
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -13974,8 +13911,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="52"/>
       <c r="E7" s="36" t="s">
         <v>108</v>
@@ -13990,7 +13927,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
@@ -14016,7 +13953,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -14024,19 +13961,19 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="99" t="str">
         <f>HYPERLINK("#'Input - Other Livestock'!A1", "Other Livestock")</f>
         <v>Other Livestock</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
@@ -14060,7 +13997,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'3.6.1.1-2 Enteric Methane'!A1", "3.6.1.1-2 Enteric Methane")</f>
         <v>3.6.1.1-2 Enteric Methane</v>
@@ -14091,15 +14028,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
         <v>1</v>
       </c>
@@ -14109,13 +14046,13 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Other Livestock'!A1", "Constants - Other Livestock")</f>
         <v>Constants - Other Livestock</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -14134,7 +14071,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -14161,7 +14098,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="str">
         <f>HYPERLINK("#'Tab template'!A1", "Tab template")</f>
         <v>Tab template</v>
@@ -14169,19 +14106,19 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="6" t="s">
         <v>124</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="52"/>
       <c r="E25" s="36" t="s">
         <v>125</v>
@@ -14199,7 +14136,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="str">
         <f>"Average number of head between " &amp; TEXT(X_Cell_Site_StartDate, "dd mmm yy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "dd mmm yy")</f>
         <v>Average number of head between 01 Jan 24 and 31 Dec 24</v>
@@ -14223,175 +14160,175 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="9:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="9:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="79"/>
     </row>
-    <row r="58" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14404,7 +14341,7 @@
     <tabColor rgb="FF008000"/>
   </sheetPr>
   <dimension ref="A1:S183"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -14426,11 +14363,11 @@
       </c>
       <c r="K1"/>
     </row>
-    <row r="2" spans="1:19" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="K2"/>
     </row>
-    <row r="3" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -14456,13 +14393,13 @@
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
     </row>
-    <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -14472,13 +14409,13 @@
         <v>Total annual methane production from enteric fermentation in other livestock</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="5" t="str" cm="1">
         <f t="array" ref="D6">EntericMethane_OtherLivestock_Equations.VEERG_3_6_1_1__1_TotalAnnualMethaneFromEntericFermentationOtherLivestock_Source()</f>
         <v>VEERG 2026: 3.6.1.1, Equation (1)</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="13" t="s">
         <v>13</v>
       </c>
@@ -14487,18 +14424,18 @@
         <v>=EntericMethane_OtherLivestock_Equations.VEERG_3_6_1_1__1_TotalAnnualMethaneFromEntericFermentationOtherLivestock</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Other Livestock'!A1", "Other Livestock")</f>
         <v>Other Livestock</v>
@@ -14511,7 +14448,7 @@
         <v>E_enteric</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="47" t="s">
         <v>8</v>
       </c>
@@ -14520,8 +14457,8 @@
         <v>t CH4</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
@@ -14541,7 +14478,7 @@
         <v>Input</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="98" t="str">
         <f>HYPERLINK("#'3.6.1.1-2 Enteric Methane'!A1", "3.6.1.1-2 Enteric Methane")</f>
         <v>3.6.1.1-2 Enteric Methane</v>
@@ -14560,7 +14497,7 @@
         <v>Constant</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="88" t="str">
         <v>j</v>
       </c>
@@ -14575,13 +14512,13 @@
         <v>Input</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
         <f>HYPERLINK("#'Constants - Other Livestock'!A1", "Constants - Other Livestock")</f>
         <v>Constants - Other Livestock</v>
@@ -14599,7 +14536,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -14625,7 +14562,7 @@
         <v>t CH4</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -14647,7 +14584,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="str">
         <f>HYPERLINK("#'Tab template'!A1", "Tab template")</f>
         <v>Tab template</v>
@@ -14669,7 +14606,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="46" t="str">
         <f>'Constants - Other Livestock'!D13</f>
         <v>Camels</v>
@@ -14687,7 +14624,7 @@
         <v>197.8</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="46" t="str">
         <f>'Constants - Other Livestock'!D14</f>
         <v>Alpacas</v>
@@ -14705,7 +14642,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="46" t="str">
         <f>'Constants - Other Livestock'!D15</f>
         <v>Horses</v>
@@ -14723,7 +14660,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="46" t="str">
         <f>'Constants - Other Livestock'!D16</f>
         <v>Mules/asses</v>
@@ -14741,7 +14678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="46" t="str">
         <f>'Constants - Other Livestock'!D17</f>
         <v>Emus/ostriches</v>
@@ -14759,8 +14696,8 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="76" t="s">
         <v>132</v>
       </c>
@@ -14774,8 +14711,8 @@
       </c>
       <c r="G28" s="41"/>
     </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="101" t="str" cm="1">
         <f t="array" ref="D30:E31">Common_Equations.Common_ConvertCH4ToCO2e_Arguments()</f>
         <v>ECH4</v>
@@ -14793,7 +14730,7 @@
         <v>t CH4</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="101" t="str">
         <v>GWPCH4</v>
       </c>
@@ -14806,8 +14743,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="41" t="s">
         <v>135</v>
       </c>
@@ -14820,156 +14757,156 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="34" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E133:G133 E138:G138 D55:F55 D60:F60 N138:P138" xr:uid="{AF7BB680-B75F-4AE8-AA2D-EDF03FCB10D8}"/>
@@ -14986,7 +14923,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:V288"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15005,10 +14942,10 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -15033,14 +14970,14 @@
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
     </row>
-    <row r="4" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -15051,21 +14988,21 @@
       </c>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="5" t="str" cm="1">
         <f t="array" ref="D6">SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Source()</f>
         <v>VEERG 2026: Table A.1.5.1</v>
       </c>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="str" cm="1">
         <f t="array" ref="D7">SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Variable()</f>
         <v>Mj</v>
       </c>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
@@ -15075,7 +15012,7 @@
       </c>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -15088,7 +15025,7 @@
       </c>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
         <f>HYPERLINK("#'Input - Other Livestock'!A1", "Other Livestock")</f>
         <v>Other Livestock</v>
@@ -15103,7 +15040,7 @@
       </c>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="1" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</f>
         <v>Goats</v>
@@ -15114,7 +15051,7 @@
       </c>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="1" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</f>
         <v>Deer</v>
@@ -15125,7 +15062,7 @@
       </c>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
@@ -15139,7 +15076,7 @@
       </c>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
         <f>HYPERLINK("#'3.6.1.1-2 Enteric Methane'!A1", "3.6.1.1-2 Enteric Methane")</f>
         <v>3.6.1.1-2 Enteric Methane</v>
@@ -15154,7 +15091,7 @@
       </c>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="1" t="str" cm="1">
         <f t="array" ref="D15">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</f>
         <v>Horses</v>
@@ -15165,7 +15102,7 @@
       </c>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="1" t="str" cm="1">
         <f t="array" ref="D16">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</f>
         <v>Mules/asses</v>
@@ -15176,7 +15113,7 @@
       </c>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
         <v>1</v>
       </c>
@@ -15190,21 +15127,21 @@
       </c>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="55" t="str">
         <f>HYPERLINK("#'Constants - Other Livestock'!A1", "Constants - Other Livestock")</f>
         <v>Constants - Other Livestock</v>
       </c>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -15215,7 +15152,7 @@
       </c>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="str">
         <f>HYPERLINK("#'Tab template'!A1", "Tab template")</f>
         <v>Tab template</v>
@@ -15226,21 +15163,21 @@
       </c>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="1" t="str" cm="1">
         <f t="array" ref="D22">SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Variable()</f>
         <v>VSj</v>
       </c>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="48" t="str" cm="1">
         <f t="array" ref="D23">SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Unit()</f>
         <v>kg VS / head / day</v>
       </c>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="34" t="s">
         <v>98</v>
       </c>
@@ -15249,7 +15186,7 @@
       </c>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="34" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</f>
         <v>Buffalo</v>
@@ -15260,7 +15197,7 @@
       </c>
       <c r="M25" s="1"/>
     </row>
-    <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="34" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</f>
         <v>Goats</v>
@@ -15271,7 +15208,7 @@
       </c>
       <c r="M26" s="1"/>
     </row>
-    <row r="27" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="34" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</f>
         <v>Deer</v>
@@ -15282,7 +15219,7 @@
       </c>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="34" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</f>
         <v>Camels</v>
@@ -15293,7 +15230,7 @@
       </c>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="34" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</f>
         <v>Alpacas</v>
@@ -15304,7 +15241,7 @@
       </c>
       <c r="M29" s="1"/>
     </row>
-    <row r="30" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="34" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</f>
         <v>Horses</v>
@@ -15315,7 +15252,7 @@
       </c>
       <c r="M30" s="1"/>
     </row>
-    <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="34" t="str" cm="1">
         <f t="array" ref="D31">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</f>
         <v>Mules/asses</v>
@@ -15326,7 +15263,7 @@
       </c>
       <c r="M31" s="1"/>
     </row>
-    <row r="32" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="34" t="str" cm="1">
         <f t="array" ref="D32">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</f>
         <v>Emus/ostriches</v>
@@ -15337,41 +15274,41 @@
       </c>
       <c r="M32" s="1"/>
     </row>
-    <row r="33" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M33" s="1"/>
     </row>
-    <row r="34" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M34" s="1"/>
     </row>
-    <row r="35" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="6" t="str" cm="1">
         <f t="array" ref="D35">SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Title()</f>
         <v>Other Livestock - Nitrogen excreted per livestock type</v>
       </c>
       <c r="M35" s="1"/>
     </row>
-    <row r="36" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="5" t="str" cm="1">
         <f t="array" ref="D36">SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Source()</f>
         <v>VEERG 2026: Table A.1.5.3</v>
       </c>
       <c r="M36" s="1"/>
     </row>
-    <row r="37" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="1" t="str" cm="1">
         <f t="array" ref="D37">SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Variable()</f>
         <v>NEj</v>
       </c>
       <c r="M37" s="1"/>
     </row>
-    <row r="38" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="48" t="str" cm="1">
         <f t="array" ref="D38">SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Unit()</f>
         <v>kg N2O / head / year</v>
       </c>
       <c r="M38" s="1"/>
     </row>
-    <row r="39" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="34" t="s">
         <v>98</v>
       </c>
@@ -15380,7 +15317,7 @@
       </c>
       <c r="M39" s="1"/>
     </row>
-    <row r="40" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="34" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</f>
         <v>Buffalo</v>
@@ -15391,7 +15328,7 @@
       </c>
       <c r="M40" s="1"/>
     </row>
-    <row r="41" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="34" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</f>
         <v>Goats</v>
@@ -15402,7 +15339,7 @@
       </c>
       <c r="M41" s="1"/>
     </row>
-    <row r="42" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="34" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</f>
         <v>Deer</v>
@@ -15413,7 +15350,7 @@
       </c>
       <c r="M42" s="1"/>
     </row>
-    <row r="43" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="34" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</f>
         <v>Camels</v>
@@ -15424,7 +15361,7 @@
       </c>
       <c r="M43" s="1"/>
     </row>
-    <row r="44" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="34" t="str" cm="1">
         <f t="array" ref="D44">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</f>
         <v>Alpacas</v>
@@ -15435,7 +15372,7 @@
       </c>
       <c r="M44" s="1"/>
     </row>
-    <row r="45" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="34" t="str" cm="1">
         <f t="array" ref="D45">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</f>
         <v>Horses</v>
@@ -15446,7 +15383,7 @@
       </c>
       <c r="M45" s="1"/>
     </row>
-    <row r="46" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="34" t="str" cm="1">
         <f t="array" ref="D46">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</f>
         <v>Mules/asses</v>
@@ -15457,7 +15394,7 @@
       </c>
       <c r="M46" s="1"/>
     </row>
-    <row r="47" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="34" t="str" cm="1">
         <f t="array" ref="D47">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</f>
         <v>Emus/ostriches</v>
@@ -15468,41 +15405,41 @@
       </c>
       <c r="M47" s="1"/>
     </row>
-    <row r="48" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M49" s="1"/>
     </row>
-    <row r="50" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="6" t="str" cm="1">
         <f t="array" ref="D50">SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Title()</f>
         <v>Other Livestock - Average Liveweights</v>
       </c>
       <c r="M50" s="1"/>
     </row>
-    <row r="51" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="5" t="str" cm="1">
         <f t="array" ref="D51">SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Source()</f>
         <v>VEERG 2026: Table A.1.5.4</v>
       </c>
       <c r="M51" s="1"/>
     </row>
-    <row r="52" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="1" t="str" cm="1">
         <f t="array" ref="D52">SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Variable()</f>
         <v>Wco</v>
       </c>
       <c r="M52" s="1"/>
     </row>
-    <row r="53" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="48" t="str" cm="1">
         <f t="array" ref="D53">SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Unit()</f>
         <v>kg</v>
       </c>
       <c r="M53" s="1"/>
     </row>
-    <row r="54" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="34" t="s">
         <v>98</v>
       </c>
@@ -15514,7 +15451,7 @@
       </c>
       <c r="M54" s="1"/>
     </row>
-    <row r="55" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="34" t="str" cm="1">
         <f t="array" ref="D55">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</f>
         <v>Buffalo</v>
@@ -15529,7 +15466,7 @@
       </c>
       <c r="M55" s="1"/>
     </row>
-    <row r="56" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="34" t="str" cm="1">
         <f t="array" ref="D56">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</f>
         <v>Goats</v>
@@ -15544,7 +15481,7 @@
       </c>
       <c r="M56" s="1"/>
     </row>
-    <row r="57" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="34" t="str" cm="1">
         <f t="array" ref="D57">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</f>
         <v>Goats</v>
@@ -15559,7 +15496,7 @@
       </c>
       <c r="M57" s="1"/>
     </row>
-    <row r="58" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="34" t="str" cm="1">
         <f t="array" ref="D58">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</f>
         <v>Deer</v>
@@ -15574,7 +15511,7 @@
       </c>
       <c r="M58" s="1"/>
     </row>
-    <row r="59" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="34" t="str" cm="1">
         <f t="array" ref="D59">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</f>
         <v>Camels</v>
@@ -15589,7 +15526,7 @@
       </c>
       <c r="M59" s="1"/>
     </row>
-    <row r="60" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="34" t="str" cm="1">
         <f t="array" ref="D60">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</f>
         <v>Alpacas</v>
@@ -15604,7 +15541,7 @@
       </c>
       <c r="M60" s="1"/>
     </row>
-    <row r="61" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="34" t="str" cm="1">
         <f t="array" ref="D61">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</f>
         <v>Horses</v>
@@ -15619,7 +15556,7 @@
       </c>
       <c r="M61" s="1"/>
     </row>
-    <row r="62" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="34" t="str" cm="1">
         <f t="array" ref="D62">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</f>
         <v>Mules/asses</v>
@@ -15634,7 +15571,7 @@
       </c>
       <c r="M62" s="1"/>
     </row>
-    <row r="63" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="34" t="str" cm="1">
         <f t="array" ref="D63">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</f>
         <v>Emus/ostriches</v>
@@ -15649,7 +15586,7 @@
       </c>
       <c r="M63" s="1"/>
     </row>
-    <row r="64" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="34" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</f>
         <v>Reference</v>
@@ -15664,41 +15601,41 @@
       </c>
       <c r="M64" s="1"/>
     </row>
-    <row r="65" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M65" s="1"/>
     </row>
-    <row r="66" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M66" s="1"/>
     </row>
-    <row r="67" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="6" t="str" cm="1">
         <f t="array" ref="D67">SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Title()</f>
         <v>Other Livestock - Fraction of waste in each manure management system</v>
       </c>
       <c r="M67" s="1"/>
     </row>
-    <row r="68" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="5" t="str" cm="1">
         <f t="array" ref="D68">SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Source()</f>
         <v>VEERG 2026: Table A.1.5.5</v>
       </c>
       <c r="M68" s="1"/>
     </row>
-    <row r="69" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="1" t="str" cm="1">
         <f t="array" ref="D69">SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Variable()</f>
         <v>MMSm</v>
       </c>
       <c r="M69" s="1"/>
     </row>
-    <row r="70" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="48" t="str" cm="1">
         <f t="array" ref="D70">SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Unit()</f>
         <v>fraction</v>
       </c>
       <c r="M70" s="1"/>
     </row>
-    <row r="71" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="34" t="s">
         <v>98</v>
       </c>
@@ -15710,7 +15647,7 @@
       </c>
       <c r="M71" s="1"/>
     </row>
-    <row r="72" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="34" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</f>
         <v>ACT</v>
@@ -15725,7 +15662,7 @@
       </c>
       <c r="M72" s="1"/>
     </row>
-    <row r="73" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D73" s="34" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</f>
         <v>NSW</v>
@@ -15740,7 +15677,7 @@
       </c>
       <c r="M73" s="1"/>
     </row>
-    <row r="74" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D74" s="34" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</f>
         <v>NT</v>
@@ -15755,7 +15692,7 @@
       </c>
       <c r="M74" s="1"/>
     </row>
-    <row r="75" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D75" s="34" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</f>
         <v>QLD</v>
@@ -15770,7 +15707,7 @@
       </c>
       <c r="M75" s="1"/>
     </row>
-    <row r="76" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D76" s="34" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</f>
         <v>SA</v>
@@ -15785,7 +15722,7 @@
       </c>
       <c r="M76" s="1"/>
     </row>
-    <row r="77" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D77" s="34" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</f>
         <v>TAS</v>
@@ -15800,7 +15737,7 @@
       </c>
       <c r="M77" s="1"/>
     </row>
-    <row r="78" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="34" t="str" cm="1">
         <f t="array" ref="D78">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</f>
         <v>VIC</v>
@@ -15815,7 +15752,7 @@
       </c>
       <c r="M78" s="1"/>
     </row>
-    <row r="79" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="34" t="str" cm="1">
         <f t="array" ref="D79">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</f>
         <v>WA</v>
@@ -15830,41 +15767,41 @@
       </c>
       <c r="M79" s="1"/>
     </row>
-    <row r="80" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M80" s="1"/>
     </row>
-    <row r="81" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M81" s="1"/>
     </row>
-    <row r="82" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="6" t="str" cm="1">
         <f t="array" ref="D82">SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Title()</f>
         <v>Other Livestock - Methane conversion factor per region</v>
       </c>
       <c r="M82" s="1"/>
     </row>
-    <row r="83" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D83" s="5" t="str" cm="1">
         <f t="array" ref="D83">SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Source()</f>
         <v>VEERG 2026: Table A.1.5.6</v>
       </c>
       <c r="M83" s="1"/>
     </row>
-    <row r="84" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D84" s="1" t="str" cm="1">
         <f t="array" ref="D84">SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Variable()</f>
         <v>MCFim</v>
       </c>
       <c r="M84" s="1"/>
     </row>
-    <row r="85" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="48" t="str" cm="1">
         <f t="array" ref="D85">SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Unit()</f>
         <v>fraction</v>
       </c>
       <c r="M85" s="1"/>
     </row>
-    <row r="86" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="34" t="s">
         <v>98</v>
       </c>
@@ -15876,7 +15813,7 @@
       </c>
       <c r="M86" s="1"/>
     </row>
-    <row r="87" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D87" s="34" t="str" cm="1">
         <f t="array" ref="D87">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</f>
         <v>ACT</v>
@@ -15891,7 +15828,7 @@
       </c>
       <c r="M87" s="1"/>
     </row>
-    <row r="88" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D88" s="34" t="str" cm="1">
         <f t="array" ref="D88">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</f>
         <v>NSW</v>
@@ -15906,7 +15843,7 @@
       </c>
       <c r="M88" s="1"/>
     </row>
-    <row r="89" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="34" t="str" cm="1">
         <f t="array" ref="D89">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</f>
         <v>NT</v>
@@ -15921,7 +15858,7 @@
       </c>
       <c r="M89" s="1"/>
     </row>
-    <row r="90" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D90" s="34" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</f>
         <v>QLD</v>
@@ -15936,7 +15873,7 @@
       </c>
       <c r="M90" s="1"/>
     </row>
-    <row r="91" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="34" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</f>
         <v>SA</v>
@@ -15951,7 +15888,7 @@
       </c>
       <c r="M91" s="1"/>
     </row>
-    <row r="92" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D92" s="34" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</f>
         <v>TAS</v>
@@ -15966,7 +15903,7 @@
       </c>
       <c r="M92" s="1"/>
     </row>
-    <row r="93" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D93" s="34" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</f>
         <v>VIC</v>
@@ -15981,7 +15918,7 @@
       </c>
       <c r="M93" s="1"/>
     </row>
-    <row r="94" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D94" s="34" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</f>
         <v>WA</v>
@@ -15996,589 +15933,589 @@
       </c>
       <c r="M94" s="1"/>
     </row>
-    <row r="95" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M95" s="1"/>
     </row>
-    <row r="96" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M96" s="1"/>
     </row>
-    <row r="97" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M97" s="1"/>
     </row>
-    <row r="98" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M98" s="1"/>
     </row>
-    <row r="99" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M99" s="1"/>
     </row>
-    <row r="100" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M100" s="1"/>
     </row>
-    <row r="101" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M101" s="1"/>
     </row>
-    <row r="102" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M102" s="1"/>
     </row>
-    <row r="103" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M103" s="1"/>
     </row>
-    <row r="104" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M104" s="1"/>
     </row>
-    <row r="105" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M105" s="1"/>
     </row>
-    <row r="106" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M106" s="1"/>
     </row>
-    <row r="107" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M107" s="1"/>
     </row>
-    <row r="108" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M108" s="1"/>
     </row>
-    <row r="109" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M109" s="1"/>
     </row>
-    <row r="110" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M110" s="1"/>
     </row>
-    <row r="111" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M111" s="1"/>
     </row>
-    <row r="112" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M112" s="1"/>
     </row>
-    <row r="113" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M113" s="1"/>
     </row>
-    <row r="114" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M114" s="1"/>
     </row>
-    <row r="115" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M115" s="1"/>
       <c r="V115" s="1"/>
     </row>
-    <row r="116" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M116" s="1"/>
       <c r="V116" s="1"/>
     </row>
-    <row r="117" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M117" s="1"/>
       <c r="V117" s="1"/>
     </row>
-    <row r="118" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M118" s="1"/>
     </row>
-    <row r="119" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M119" s="1"/>
     </row>
-    <row r="120" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M120" s="1"/>
     </row>
-    <row r="121" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M121" s="1"/>
     </row>
-    <row r="122" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M122" s="1"/>
     </row>
-    <row r="123" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M123" s="1"/>
     </row>
-    <row r="124" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M124" s="21"/>
     </row>
-    <row r="125" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M125" s="21"/>
     </row>
-    <row r="126" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M126" s="21"/>
     </row>
-    <row r="127" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M127" s="21"/>
     </row>
-    <row r="128" spans="13:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="13:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M128" s="21"/>
     </row>
-    <row r="129" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M129" s="21"/>
     </row>
-    <row r="130" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M130" s="21"/>
     </row>
-    <row r="131" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M131" s="21"/>
     </row>
-    <row r="132" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M132" s="21"/>
     </row>
-    <row r="133" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M133" s="21"/>
     </row>
-    <row r="134" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M134" s="21"/>
     </row>
-    <row r="135" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M135" s="21"/>
     </row>
-    <row r="136" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M136" s="21"/>
     </row>
-    <row r="137" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M137" s="21"/>
     </row>
-    <row r="138" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M138" s="21"/>
     </row>
-    <row r="139" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M139" s="21"/>
     </row>
-    <row r="140" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M140" s="21"/>
     </row>
-    <row r="141" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M141" s="21"/>
     </row>
-    <row r="142" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M142" s="21"/>
     </row>
-    <row r="143" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M143" s="21"/>
     </row>
-    <row r="144" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M144" s="21"/>
     </row>
-    <row r="145" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M145" s="21"/>
     </row>
-    <row r="146" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M146" s="21"/>
     </row>
-    <row r="147" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M147" s="21"/>
     </row>
-    <row r="148" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M148" s="21"/>
     </row>
-    <row r="149" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M149" s="21"/>
     </row>
-    <row r="150" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M150" s="21"/>
     </row>
-    <row r="151" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M151" s="21"/>
     </row>
-    <row r="152" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M152" s="21"/>
     </row>
-    <row r="153" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M153" s="21"/>
     </row>
-    <row r="154" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M154" s="21"/>
     </row>
-    <row r="155" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M155" s="21"/>
     </row>
-    <row r="156" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M156" s="21"/>
     </row>
-    <row r="157" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M157" s="21"/>
     </row>
-    <row r="158" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M158" s="21"/>
     </row>
-    <row r="159" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M159" s="21"/>
     </row>
-    <row r="160" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M160" s="21"/>
     </row>
-    <row r="161" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M161" s="21"/>
     </row>
-    <row r="162" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M162" s="21"/>
     </row>
-    <row r="163" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M163" s="21"/>
     </row>
-    <row r="164" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M164" s="21"/>
     </row>
-    <row r="165" spans="13:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="13:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M165" s="21"/>
     </row>
-    <row r="166" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M166" s="21"/>
     </row>
-    <row r="167" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M167" s="21"/>
     </row>
-    <row r="168" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M168" s="21"/>
     </row>
-    <row r="169" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M169" s="21"/>
     </row>
-    <row r="170" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M170" s="21"/>
     </row>
-    <row r="171" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M171" s="21"/>
     </row>
-    <row r="172" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M172" s="21"/>
     </row>
-    <row r="173" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M173" s="21"/>
     </row>
-    <row r="174" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M174" s="21"/>
     </row>
-    <row r="175" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M175" s="21"/>
     </row>
-    <row r="176" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M176" s="21"/>
     </row>
-    <row r="177" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M177" s="21"/>
     </row>
-    <row r="178" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M178" s="21"/>
     </row>
-    <row r="179" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M179" s="21"/>
     </row>
-    <row r="180" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M180" s="21"/>
     </row>
-    <row r="181" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M181" s="21"/>
     </row>
-    <row r="182" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M182" s="21"/>
     </row>
-    <row r="183" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M183" s="21"/>
     </row>
-    <row r="184" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M184" s="21"/>
     </row>
-    <row r="185" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M185" s="21"/>
     </row>
-    <row r="186" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M186" s="21"/>
     </row>
-    <row r="187" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M187" s="21"/>
     </row>
-    <row r="188" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M188" s="21"/>
     </row>
-    <row r="189" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M189" s="21"/>
     </row>
-    <row r="190" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M190" s="21"/>
     </row>
-    <row r="191" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M191" s="21"/>
     </row>
-    <row r="192" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M192" s="21"/>
     </row>
-    <row r="193" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M193" s="21"/>
     </row>
-    <row r="194" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M194" s="21"/>
     </row>
-    <row r="195" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M195" s="21"/>
     </row>
-    <row r="196" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M196" s="21"/>
     </row>
-    <row r="197" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M197" s="21"/>
     </row>
-    <row r="198" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M198" s="21"/>
     </row>
-    <row r="199" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M199" s="21"/>
     </row>
-    <row r="200" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M200" s="21"/>
     </row>
-    <row r="201" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M201" s="21"/>
     </row>
-    <row r="202" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M202" s="21"/>
     </row>
-    <row r="203" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M203" s="21"/>
     </row>
-    <row r="204" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M204" s="21"/>
     </row>
-    <row r="205" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M205" s="21"/>
     </row>
-    <row r="206" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M206" s="21"/>
     </row>
-    <row r="207" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M207" s="21"/>
     </row>
-    <row r="208" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M208" s="21"/>
     </row>
-    <row r="209" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M209" s="21"/>
     </row>
-    <row r="210" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M210" s="21"/>
     </row>
-    <row r="211" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M211" s="21"/>
     </row>
-    <row r="212" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M212" s="21"/>
     </row>
-    <row r="213" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M213" s="21"/>
     </row>
-    <row r="214" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M214" s="21"/>
     </row>
-    <row r="215" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M215" s="21"/>
     </row>
-    <row r="216" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M216" s="21"/>
     </row>
-    <row r="217" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M217" s="21"/>
     </row>
-    <row r="218" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M218" s="21"/>
     </row>
-    <row r="219" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M219" s="21"/>
     </row>
-    <row r="220" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M220" s="21"/>
     </row>
-    <row r="221" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M221" s="21"/>
     </row>
-    <row r="222" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M222" s="21"/>
     </row>
-    <row r="223" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M223" s="21"/>
     </row>
-    <row r="224" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M224" s="21"/>
     </row>
-    <row r="225" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M225" s="21"/>
     </row>
-    <row r="226" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M226" s="21"/>
     </row>
-    <row r="227" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M227" s="21"/>
     </row>
-    <row r="228" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M228" s="21"/>
     </row>
-    <row r="229" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M229" s="21"/>
     </row>
-    <row r="230" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M230" s="21"/>
     </row>
-    <row r="231" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M231" s="21"/>
     </row>
-    <row r="232" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M232" s="21"/>
     </row>
-    <row r="233" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M233" s="21"/>
     </row>
-    <row r="234" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M234" s="21"/>
     </row>
-    <row r="235" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M235" s="21"/>
     </row>
-    <row r="236" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M236" s="21"/>
     </row>
-    <row r="237" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M237" s="21"/>
     </row>
-    <row r="238" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M238" s="21"/>
     </row>
-    <row r="239" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M239" s="21"/>
     </row>
-    <row r="240" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M240" s="21"/>
     </row>
-    <row r="241" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M241" s="21"/>
     </row>
-    <row r="242" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M242" s="21"/>
     </row>
-    <row r="243" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M243" s="21"/>
     </row>
-    <row r="244" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M244" s="21"/>
     </row>
-    <row r="245" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M245" s="21"/>
     </row>
-    <row r="246" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M246" s="21"/>
     </row>
-    <row r="247" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M247" s="21"/>
     </row>
-    <row r="248" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M248" s="21"/>
     </row>
-    <row r="249" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M249" s="21"/>
     </row>
-    <row r="250" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M250" s="21"/>
     </row>
-    <row r="251" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M251" s="21"/>
     </row>
-    <row r="252" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M252" s="21"/>
     </row>
-    <row r="253" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M253" s="21"/>
     </row>
-    <row r="254" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M254" s="21"/>
     </row>
-    <row r="255" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M255" s="21"/>
     </row>
-    <row r="256" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M256" s="21"/>
     </row>
-    <row r="257" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M257" s="21"/>
     </row>
-    <row r="258" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M258" s="21"/>
     </row>
-    <row r="259" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M259" s="21"/>
     </row>
-    <row r="260" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M260" s="21"/>
     </row>
-    <row r="261" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M261" s="21"/>
     </row>
-    <row r="262" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="262" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M262" s="21"/>
     </row>
-    <row r="263" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M263" s="21"/>
     </row>
-    <row r="264" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M264" s="21"/>
     </row>
-    <row r="265" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M265" s="21"/>
     </row>
-    <row r="266" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M266" s="21"/>
     </row>
-    <row r="267" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M267" s="21"/>
     </row>
-    <row r="268" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M268" s="21"/>
     </row>
-    <row r="269" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M269" s="21"/>
     </row>
-    <row r="270" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M270" s="21"/>
     </row>
-    <row r="271" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M271" s="21"/>
     </row>
-    <row r="272" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M272" s="21"/>
     </row>
-    <row r="273" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M273" s="21"/>
     </row>
-    <row r="274" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M274" s="21"/>
     </row>
-    <row r="275" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M275" s="21"/>
     </row>
-    <row r="276" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M276" s="21"/>
     </row>
-    <row r="277" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="277" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M277" s="21"/>
     </row>
-    <row r="278" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="278" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M278" s="21"/>
     </row>
-    <row r="279" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M279" s="21"/>
     </row>
-    <row r="280" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M280" s="21"/>
     </row>
-    <row r="281" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M281" s="21"/>
     </row>
-    <row r="282" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M282" s="21"/>
     </row>
-    <row r="283" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M283" s="21"/>
     </row>
-    <row r="284" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M284" s="21"/>
     </row>
-    <row r="285" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M285" s="21"/>
     </row>
-    <row r="286" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M286" s="21"/>
     </row>
-    <row r="287" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="287" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M287" s="21"/>
     </row>
-    <row r="288" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="288" spans="13:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="M288" s="21"/>
     </row>
   </sheetData>
@@ -16600,7 +16537,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="7" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="7" customWidth="1"/>
@@ -16633,10 +16570,10 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -16663,11 +16600,11 @@
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="3"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="6" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -16675,7 +16612,7 @@
       </c>
       <c r="BM5" s="3"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="104" t="s">
         <v>1</v>
       </c>
@@ -16689,7 +16626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="55" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -16707,7 +16644,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -16725,7 +16662,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="34" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16740,7 +16677,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="34" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16755,7 +16692,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="34" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16771,7 +16708,7 @@
       </c>
       <c r="BM11" s="3"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="34" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16787,7 +16724,7 @@
       </c>
       <c r="BM12" s="3"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="34" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16802,7 +16739,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="34" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16817,129 +16754,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="6" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="5" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="34" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="34" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="34" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="34" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="34" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="34" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="34" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="34" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="34" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="34" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="34" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="6" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="5" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="34" t="s">
         <v>14</v>
@@ -16948,7 +16885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="34" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16959,7 +16896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="34" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16970,7 +16907,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="34" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16981,7 +16918,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="34" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16992,7 +16929,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="34" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17003,7 +16940,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="34" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17014,7 +16951,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="34" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17025,24 +16962,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="6" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="5" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="34" t="s">
         <v>14</v>
@@ -17060,7 +16997,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="34" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17083,7 +17020,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="34" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17106,7 +17043,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="34" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17129,7 +17066,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="34" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17152,7 +17089,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="34" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17175,7 +17112,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="34" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17198,7 +17135,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="34" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17221,49 +17158,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="6" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="5" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="49" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="49" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="49" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="34" t="s">
         <v>5</v>
@@ -17272,7 +17209,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="34" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17283,7 +17220,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="34" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17294,7 +17231,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="34" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17305,7 +17242,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="34" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17316,7 +17253,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="34" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17327,7 +17264,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="34" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17338,7 +17275,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="34" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17349,7 +17286,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="34" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17360,7 +17297,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="34" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17371,7 +17308,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="34" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17382,7 +17319,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="34" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17393,7 +17330,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="34" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17404,7 +17341,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="34" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17415,7 +17352,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="34" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17426,64 +17363,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="6" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="5" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="49" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="49" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="49" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="49" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="49" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="34" t="s">
         <v>5</v>
@@ -17535,7 +17472,7 @@
       </c>
       <c r="T89" s="34"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="34" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17603,7 +17540,7 @@
       </c>
       <c r="T90" s="34"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="34" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17671,7 +17608,7 @@
       </c>
       <c r="T91" s="34"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="34" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17739,7 +17676,7 @@
       </c>
       <c r="T92" s="34"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="34" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17807,7 +17744,7 @@
       </c>
       <c r="T93" s="34"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="34" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17875,7 +17812,7 @@
       </c>
       <c r="T94" s="34"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="34" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17943,7 +17880,7 @@
       </c>
       <c r="T95" s="34"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="34" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18011,7 +17948,7 @@
       </c>
       <c r="T96" s="34"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="34" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18079,66 +18016,66 @@
       </c>
       <c r="T97" s="34"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="48" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="48" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="48" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="48" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="48"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="6" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="5" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="49" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="34" t="s">
         <v>39</v>
@@ -18153,7 +18090,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="34" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18172,7 +18109,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="34" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18191,7 +18128,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="34" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18210,13 +18147,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="6" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -18224,7 +18161,7 @@
       </c>
       <c r="BN115" s="7"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="5" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -18232,7 +18169,7 @@
       </c>
       <c r="BN116" s="7"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="49" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -18240,11 +18177,11 @@
       </c>
       <c r="BN117" s="7"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="7"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="34" t="s">
         <v>42</v>
@@ -18260,7 +18197,7 @@
       </c>
       <c r="BN119" s="7"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="34" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18280,7 +18217,7 @@
       </c>
       <c r="BN120" s="7"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="34" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18300,31 +18237,31 @@
       </c>
       <c r="BN121" s="7"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="7"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="6" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="5" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="34" t="s">
         <v>44</v>
@@ -18333,7 +18270,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="34" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18344,7 +18281,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="34" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18355,13 +18292,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="6" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -18369,7 +18306,7 @@
       </c>
       <c r="E132" s="21"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="5" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -18377,7 +18314,7 @@
       </c>
       <c r="E133" s="21"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>55</v>
@@ -18386,7 +18323,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18397,7 +18334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18408,10 +18345,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="7"/>
       <c r="BO138" s="7"/>
@@ -18426,7 +18363,7 @@
       <c r="BX138" s="7"/>
       <c r="BY138" s="7"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="6" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -18445,7 +18382,7 @@
       <c r="BX139" s="7"/>
       <c r="BY139" s="7"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="5" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -18464,7 +18401,7 @@
       <c r="BX140" s="7"/>
       <c r="BY140" s="7"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="49" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -18472,7 +18409,7 @@
       </c>
       <c r="BN141" s="7"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="34" t="s">
         <v>70</v>
@@ -18482,7 +18419,7 @@
       </c>
       <c r="BN142" s="7"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="34" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18494,7 +18431,7 @@
       </c>
       <c r="BN143" s="7"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18506,7 +18443,7 @@
       </c>
       <c r="BN144" s="7"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18518,7 +18455,7 @@
       </c>
       <c r="BN145" s="7"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18530,7 +18467,7 @@
       </c>
       <c r="BN146" s="7"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18542,15 +18479,15 @@
       </c>
       <c r="BN147" s="7"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="7"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="7"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="6" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -18558,7 +18495,7 @@
       </c>
       <c r="BN150" s="7"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="5" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -18566,11 +18503,11 @@
       </c>
       <c r="BN151" s="7"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="7"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="34" t="s">
         <v>46</v>
@@ -18590,7 +18527,7 @@
       <c r="BL153" s="3"/>
       <c r="BM153" s="3"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="34" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18612,7 +18549,7 @@
       <c r="BL154" s="3"/>
       <c r="BM154" s="3"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="34" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18634,7 +18571,7 @@
       <c r="BL155" s="3"/>
       <c r="BM155" s="3"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="34" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18645,7 +18582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="34" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18656,7 +18593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="34" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18667,34 +18604,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="6" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="21"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="5" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="21"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="5" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="21"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="21" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -18703,17 +18640,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="7"/>
       <c r="BO165" s="7"/>
       <c r="BP165" s="7"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="7"/>
       <c r="BO166" s="7"/>
       <c r="BP166" s="7"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="6" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -18722,7 +18659,7 @@
       <c r="BO167" s="7"/>
       <c r="BP167" s="7"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="5" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -18731,7 +18668,7 @@
       <c r="BO168" s="7"/>
       <c r="BP168" s="7"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="5" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -18740,7 +18677,7 @@
       <c r="BO169" s="7"/>
       <c r="BP169" s="7"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -18752,17 +18689,17 @@
       <c r="BO170" s="7"/>
       <c r="BP170" s="7"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="7"/>
       <c r="BO171" s="7"/>
       <c r="BP171" s="7"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="7"/>
       <c r="BO172" s="7"/>
       <c r="BP172" s="7"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="6" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -18771,7 +18708,7 @@
       <c r="BO173" s="7"/>
       <c r="BP173" s="7"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="5" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -18780,7 +18717,7 @@
       <c r="BO174" s="7"/>
       <c r="BP174" s="7"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -18793,17 +18730,17 @@
       <c r="BO175" s="7"/>
       <c r="BP175" s="7"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="7"/>
       <c r="BO176" s="7"/>
       <c r="BP176" s="7"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="7"/>
       <c r="BO177" s="7"/>
       <c r="BP177" s="7"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="6" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -18812,7 +18749,7 @@
       <c r="BO178" s="7"/>
       <c r="BP178" s="7"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="5" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -18821,39 +18758,39 @@
       <c r="BO179" s="7"/>
       <c r="BP179" s="7"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="48" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="49" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="49" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="49" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="49" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="49" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="34" t="s">
         <v>63</v>
       </c>
@@ -18870,7 +18807,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="34" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -18892,7 +18829,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="34" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -18914,7 +18851,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="34" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -18936,7 +18873,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="34" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -18958,7 +18895,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="34" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -18980,7 +18917,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="34" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -19002,7 +18939,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="34" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -19024,7 +18961,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="34" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -19046,7 +18983,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="34" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -19068,7 +19005,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="34" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -19090,7 +19027,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="34" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -19112,7 +19049,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="34" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -19134,7 +19071,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="34" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -19156,31 +19093,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="6" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="5" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="49" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="48" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="34" t="s">
         <v>5</v>
       </c>
@@ -19188,7 +19125,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="34" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -19198,7 +19135,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -19208,13 +19145,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="34" t="s">
         <v>72</v>
       </c>
@@ -19222,7 +19159,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="34" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -19232,7 +19169,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -19242,7 +19179,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -19252,7 +19189,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -19262,7 +19199,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -19272,7 +19209,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -19282,7 +19219,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -19292,7 +19229,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -19302,7 +19239,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -19312,7 +19249,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -19322,7 +19259,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -19332,7 +19269,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -19342,25 +19279,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="6" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="5" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="49" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="34" t="s">
         <v>38</v>
       </c>
@@ -19410,7 +19347,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="34" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19476,7 +19413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19542,7 +19479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19608,7 +19545,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19674,7 +19611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19740,7 +19677,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19806,7 +19743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19872,7 +19809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19938,7 +19875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20004,7 +19941,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20070,7 +20007,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20136,7 +20073,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20202,7 +20139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20268,7 +20205,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20334,7 +20271,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20400,7 +20337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20466,7 +20403,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20532,7 +20469,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20598,7 +20535,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20664,31 +20601,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="6" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="5" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="48" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="34" t="s">
         <v>137</v>
       </c>
@@ -20696,7 +20633,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="34" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -20706,7 +20643,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -20716,17 +20653,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:6" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="34" t="s">
         <v>142</v>
       </c>
@@ -20737,7 +20674,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="34" t="s">
         <v>145</v>
       </c>
@@ -20748,7 +20685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="34" t="s">
         <v>147</v>
       </c>
@@ -20759,7 +20696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="34" t="s">
         <v>149</v>
       </c>
@@ -20770,7 +20707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="34" t="s">
         <v>151</v>
       </c>
@@ -20781,7 +20718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="34" t="s">
         <v>153</v>
       </c>
@@ -20792,12 +20729,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="34" t="s">
         <v>142</v>
       </c>
@@ -20808,7 +20745,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="34" t="s">
         <v>156</v>
       </c>
@@ -20819,7 +20756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="34" t="s">
         <v>158</v>
       </c>
@@ -20830,7 +20767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="34" t="s">
         <v>160</v>
       </c>
@@ -20841,7 +20778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="34" t="s">
         <v>162</v>
       </c>
@@ -20852,7 +20789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="34" t="s">
         <v>164</v>
       </c>
@@ -20863,12 +20800,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="34" t="s">
         <v>142</v>
       </c>
@@ -20879,7 +20816,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="34" t="s">
         <v>167</v>
       </c>
@@ -20890,7 +20827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="34" t="s">
         <v>169</v>
       </c>
@@ -20901,7 +20838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="34" t="s">
         <v>171</v>
       </c>
@@ -20912,7 +20849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="34" t="s">
         <v>173</v>
       </c>
@@ -20923,7 +20860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="34" t="s">
         <v>175</v>
       </c>
@@ -20934,12 +20871,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="34" t="s">
         <v>142</v>
       </c>
@@ -20950,7 +20887,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="34" t="s">
         <v>178</v>
       </c>
@@ -20961,7 +20898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="34" t="s">
         <v>180</v>
       </c>
@@ -20972,7 +20909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="34" t="s">
         <v>182</v>
       </c>
@@ -20983,7 +20920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="34" t="s">
         <v>184</v>
       </c>
@@ -20994,7 +20931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="34" t="s">
         <v>186</v>
       </c>
@@ -21040,31 +20977,31 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="104" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="17" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="55" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
